--- a/04_Figures/F06_prediction/modules/T2/ridge/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/T2/ridge/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -171,12 +171,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -569,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -602,7 +596,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
@@ -614,16 +608,16 @@
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.626865671641791</v>
+        <v>0.601990049751244</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.182929066257523</v>
+        <v>-0.213892400402001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.144858181970065</v>
+        <v>0.23037941355076</v>
       </c>
     </row>
     <row r="4">
@@ -643,16 +637,16 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.699006353268975</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -676,28 +670,28 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.699006353268975</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.995024875621891</v>
+        <v>0.278606965174129</v>
       </c>
       <c r="K5" t="n">
-        <v>0.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.177497034864707</v>
+        <v>-0.186874216265582</v>
       </c>
       <c r="M5" t="n">
-        <v>0.094754810700925</v>
+        <v>0.158816453869165</v>
       </c>
     </row>
     <row r="6">
@@ -717,16 +711,16 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.715040697112028</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -750,28 +744,28 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.715040697112028</v>
+        <v>-0.147959183673469</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.996428571428571</v>
+        <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.995024875621891</v>
+        <v>0.646766169154229</v>
       </c>
       <c r="K7" t="n">
-        <v>0.27363184079602</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.175155971759556</v>
+        <v>-0.17807021158207</v>
       </c>
       <c r="M7" t="n">
-        <v>0.104032302555095</v>
+        <v>0.157211820077608</v>
       </c>
     </row>
     <row r="8">
@@ -791,16 +785,16 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.212729497337323</v>
+        <v>-0.199379461417974</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.85</v>
+        <v>-0.95</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -824,28 +818,28 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.212729497337323</v>
+        <v>-0.199379461417974</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.85</v>
+        <v>-0.95</v>
       </c>
       <c r="J9" t="n">
-        <v>0.800995024875622</v>
+        <v>0.796019900497512</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0746268656716418</v>
+        <v>0.134328358208955</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.182161606052445</v>
+        <v>-0.189885865350537</v>
       </c>
       <c r="M9" t="n">
-        <v>0.112078127039529</v>
+        <v>0.109945826210824</v>
       </c>
     </row>
     <row r="10">
@@ -865,13 +859,13 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.155177822520187</v>
+        <v>-0.163372537235504</v>
       </c>
       <c r="I10" t="n">
         <v>-0.988350744592826</v>
@@ -898,28 +892,28 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.155177822520187</v>
+        <v>-0.163372537235504</v>
       </c>
       <c r="I11" t="n">
         <v>-0.988350744592826</v>
       </c>
       <c r="J11" t="n">
-        <v>0.686567164179104</v>
+        <v>0.706467661691542</v>
       </c>
       <c r="K11" t="n">
-        <v>0.293532338308458</v>
+        <v>0.323383084577114</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.182520464354934</v>
+        <v>-0.177039435008036</v>
       </c>
       <c r="M11" t="n">
-        <v>0.147564803743332</v>
+        <v>0.147861165867736</v>
       </c>
     </row>
     <row r="12">
@@ -939,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -972,7 +966,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
@@ -984,16 +978,16 @@
         <v>-1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.582089552238806</v>
+        <v>0.447761194029851</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.159882448369399</v>
+        <v>-0.228498519058374</v>
       </c>
       <c r="M13" t="n">
-        <v>0.00142423226793302</v>
+        <v>0.313578341092822</v>
       </c>
     </row>
   </sheetData>
@@ -1026,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.764998244314637</v>
+        <v>-0.935022684570668</v>
       </c>
     </row>
     <row r="3">
@@ -1037,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.345222245773735</v>
+        <v>-0.433696522259098</v>
       </c>
     </row>
     <row r="4">
@@ -1059,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.15613170957792</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.164590183438248</v>
+        <v>-0.189817403557402</v>
       </c>
     </row>
     <row r="7">
@@ -1081,7 +1075,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.175260974517189</v>
+        <v>-0.172449395583964</v>
       </c>
     </row>
     <row r="8">
@@ -1092,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.118769725607215</v>
+        <v>-0.0803457602167073</v>
       </c>
     </row>
     <row r="9">
@@ -1103,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.382312279981776</v>
+        <v>-0.355111470507478</v>
       </c>
     </row>
     <row r="10">
@@ -1125,7 +1119,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.191874099680848</v>
+        <v>-0.160052483789575</v>
       </c>
     </row>
     <row r="12">
@@ -1147,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.220436435040925</v>
+        <v>-0.28881020773365</v>
       </c>
     </row>
     <row r="14">
@@ -1158,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.211057345889452</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="15">
@@ -1202,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.24438976665065</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.178247296080995</v>
+        <v>-0.199010344815343</v>
       </c>
     </row>
     <row r="20">
@@ -1224,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.173455885231348</v>
+        <v>-0.194774973546918</v>
       </c>
     </row>
     <row r="21">
@@ -1257,7 +1251,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.10314882482324</v>
       </c>
     </row>
     <row r="24">
@@ -1268,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.230300853554934</v>
+        <v>-0.215732779813112</v>
       </c>
     </row>
     <row r="25">
@@ -1290,7 +1284,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0400787854607014</v>
+        <v>0.176671929016744</v>
       </c>
     </row>
     <row r="27">
@@ -1345,7 +1339,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.219655235489467</v>
+        <v>-0.150875406134959</v>
       </c>
     </row>
     <row r="32">
@@ -1378,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.292643886187798</v>
+        <v>-0.221953991367333</v>
       </c>
     </row>
     <row r="35">
@@ -1455,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>0.00595651294342903</v>
+        <v>-0.18120445809758</v>
       </c>
     </row>
     <row r="42">
@@ -1510,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.163400345634976</v>
       </c>
     </row>
     <row r="47">
@@ -1521,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.513615674633305</v>
       </c>
     </row>
     <row r="48">
@@ -1532,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2989568873984</v>
+        <v>-0.274467119356355</v>
       </c>
     </row>
     <row r="49">
@@ -1543,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.247012635366373</v>
+        <v>-0.18604546923723</v>
       </c>
     </row>
     <row r="50">
@@ -1554,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.296400663073928</v>
       </c>
     </row>
     <row r="51">
@@ -1565,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.155426832460057</v>
       </c>
     </row>
     <row r="52">
@@ -1587,7 +1581,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.736743939839279</v>
+        <v>-0.348213423324987</v>
       </c>
     </row>
     <row r="54">
@@ -1598,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.217301922483732</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="55">
@@ -1609,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.65857789721947</v>
       </c>
     </row>
     <row r="56">
@@ -1631,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.218505861671044</v>
       </c>
     </row>
     <row r="58">
@@ -1664,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.22830653485061</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="61">
@@ -1697,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.190120879773732</v>
+        <v>-0.156686001034825</v>
       </c>
     </row>
     <row r="64">
@@ -1741,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.255061390166865</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="68">
@@ -1763,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.214343524629947</v>
       </c>
     </row>
     <row r="70">
@@ -1774,7 +1768,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.170020772102563</v>
+        <v>-0.19493735583349</v>
       </c>
     </row>
     <row r="71">
@@ -1785,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.15620056024092</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="72">
@@ -1796,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.148616313765084</v>
+        <v>-0.157583334260896</v>
       </c>
     </row>
     <row r="73">
@@ -1807,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.256417907740979</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="74">
@@ -1818,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.162671294793772</v>
+        <v>-0.199638908298686</v>
       </c>
     </row>
     <row r="75">
@@ -1840,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.192831219598223</v>
+        <v>-0.212706770389824</v>
       </c>
     </row>
     <row r="77">
@@ -1851,7 +1845,7 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.189350676392446</v>
+        <v>-0.0924142326758219</v>
       </c>
     </row>
     <row r="78">
@@ -1895,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.202487595622475</v>
+        <v>0.140718773373598</v>
       </c>
     </row>
     <row r="82">
@@ -1906,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.0468359431833345</v>
+        <v>-0.139613437213756</v>
       </c>
     </row>
     <row r="83">
@@ -1917,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.254368643407212</v>
+        <v>-0.257159949762849</v>
       </c>
     </row>
     <row r="84">
@@ -1939,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.548883062780879</v>
+        <v>-0.647908208641467</v>
       </c>
     </row>
     <row r="86">
@@ -1950,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.169348924451231</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="87">
@@ -1961,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.223950160131093</v>
+        <v>-0.194286505494159</v>
       </c>
     </row>
     <row r="88">
@@ -2016,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.35118870014677</v>
+        <v>-0.985572121676721</v>
       </c>
     </row>
     <row r="93">
@@ -2027,7 +2021,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.607784761090956</v>
       </c>
     </row>
     <row r="94">
@@ -2049,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.148910730098258</v>
+        <v>0.00985565625956764</v>
       </c>
     </row>
     <row r="96">
@@ -2060,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.30787213191219</v>
+        <v>-0.251371273260019</v>
       </c>
     </row>
     <row r="97">
@@ -2071,7 +2065,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.196644195707505</v>
+        <v>-0.203457877383596</v>
       </c>
     </row>
     <row r="98">
@@ -2082,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>0.119323742158067</v>
+        <v>-0.284407229741842</v>
       </c>
     </row>
     <row r="99">
@@ -2104,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.181937049467063</v>
+        <v>-0.200914337898032</v>
       </c>
     </row>
     <row r="101">
@@ -2115,7 +2109,7 @@
         <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.168622710196017</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="102">
@@ -2126,7 +2120,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.330882750019038</v>
+        <v>-0.194412925687557</v>
       </c>
     </row>
     <row r="103">
@@ -2137,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.270891674634617</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="104">
@@ -2159,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.248388630032034</v>
+        <v>-0.176189707588715</v>
       </c>
     </row>
     <row r="106">
@@ -2170,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.0699864571427609</v>
+        <v>-0.107312119253639</v>
       </c>
     </row>
     <row r="107">
@@ -2181,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.184209165275743</v>
+        <v>-0.330235311807092</v>
       </c>
     </row>
     <row r="108">
@@ -2192,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.159392645664083</v>
+        <v>-0.151593346908305</v>
       </c>
     </row>
     <row r="109">
@@ -2203,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>0.132631314457491</v>
+        <v>-0.870049929761236</v>
       </c>
     </row>
     <row r="110">
@@ -2236,7 +2230,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.255791605684865</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="113">
@@ -2269,7 +2263,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.264109986482267</v>
+        <v>-0.476435421398988</v>
       </c>
     </row>
     <row r="116">
@@ -2280,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.149722162940616</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2285,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.179501673652029</v>
+        <v>-0.159639527341396</v>
       </c>
     </row>
     <row r="118">
@@ -2302,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.153611384836127</v>
+        <v>-0.156153870279741</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2329,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.147972752974589</v>
       </c>
     </row>
     <row r="122">
@@ -2346,7 +2340,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.26153341842161</v>
+        <v>-0.150639399265063</v>
       </c>
     </row>
     <row r="123">
@@ -2390,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.173650296365912</v>
+        <v>-0.172202237788261</v>
       </c>
     </row>
     <row r="127">
@@ -2401,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.153825329936372</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="128">
@@ -2412,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.377370392324934</v>
       </c>
     </row>
     <row r="129">
@@ -2423,7 +2417,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-1.70769536300364</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="130">
@@ -2434,7 +2428,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.0365657132473454</v>
+        <v>-0.0673549827478224</v>
       </c>
     </row>
     <row r="131">
@@ -2445,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.449559954777629</v>
       </c>
     </row>
     <row r="132">
@@ -2456,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.222636103785554</v>
       </c>
     </row>
     <row r="133">
@@ -2500,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.165333084826469</v>
       </c>
     </row>
     <row r="137">
@@ -2522,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.26647187162365</v>
+        <v>-0.326027400758098</v>
       </c>
     </row>
     <row r="139">
@@ -2566,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.184000446486112</v>
+        <v>-0.344454363358453</v>
       </c>
     </row>
     <row r="143">
@@ -2599,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.277800776307814</v>
+        <v>-0.365794420327888</v>
       </c>
     </row>
     <row r="146">
@@ -2610,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.337465400738867</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="147">
@@ -2621,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.149184962782306</v>
       </c>
     </row>
     <row r="148">
@@ -2643,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.295054417362166</v>
+        <v>-0.161542398158655</v>
       </c>
     </row>
     <row r="150">
@@ -2676,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.275515409575367</v>
+        <v>-0.273104054768973</v>
       </c>
     </row>
     <row r="153">
@@ -2687,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.170048074135444</v>
+        <v>-0.224985404480847</v>
       </c>
     </row>
     <row r="154">
@@ -2698,7 +2692,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.90164956021912</v>
       </c>
     </row>
     <row r="155">
@@ -2709,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.310561282060741</v>
+        <v>-0.251527572399169</v>
       </c>
     </row>
     <row r="156">
@@ -2731,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0553954953211435</v>
+        <v>-0.209149320766208</v>
       </c>
     </row>
     <row r="158">
@@ -2797,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.277271471899314</v>
+        <v>-0.54093364339803</v>
       </c>
     </row>
     <row r="164">
@@ -2819,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.181379872694093</v>
+        <v>-0.187601087219962</v>
       </c>
     </row>
     <row r="166">
@@ -2841,7 +2835,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.187605582943951</v>
+        <v>-0.192447782750884</v>
       </c>
     </row>
     <row r="168">
@@ -2852,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.34228778638668</v>
+        <v>-0.172385875750786</v>
       </c>
     </row>
     <row r="169">
@@ -2863,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.158512848681235</v>
+        <v>-0.166048487248075</v>
       </c>
     </row>
     <row r="170">
@@ -3017,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.17570800991488</v>
+        <v>-0.238799112755311</v>
       </c>
     </row>
     <row r="184">
@@ -3039,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>0.0703195230487224</v>
+        <v>0.320747050222774</v>
       </c>
     </row>
     <row r="186">
@@ -3050,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.182571276631778</v>
+        <v>-1.21373807565933</v>
       </c>
     </row>
     <row r="187">
@@ -3061,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.493549731062737</v>
+        <v>-0.599011023020287</v>
       </c>
     </row>
     <row r="188">
@@ -3072,7 +3066,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.307324301983938</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="189">
@@ -3083,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0189307710857619</v>
+        <v>-0.123567236054055</v>
       </c>
     </row>
     <row r="190">
@@ -3105,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.15482916359726</v>
+        <v>-0.132547202734647</v>
       </c>
     </row>
     <row r="192">
@@ -3116,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.273809000601736</v>
+        <v>-0.157065994967983</v>
       </c>
     </row>
     <row r="193">
@@ -3127,7 +3121,7 @@
         <v>16</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.238248117484928</v>
       </c>
     </row>
     <row r="194">
@@ -3138,7 +3132,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.156786931083335</v>
+        <v>-0.157647399673124</v>
       </c>
     </row>
     <row r="195">
@@ -3149,7 +3143,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.162559529710236</v>
+        <v>-0.149193657356305</v>
       </c>
     </row>
     <row r="196">
@@ -3237,7 +3231,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>0.0366956089730912</v>
+        <v>-0.126965838874179</v>
       </c>
     </row>
     <row r="204">
@@ -3248,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.166203251617232</v>
       </c>
     </row>
     <row r="205">
@@ -3270,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.26024930454328</v>
+        <v>-0.159161215306513</v>
       </c>
     </row>
     <row r="207">
@@ -3281,7 +3275,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.149625686587399</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="208">
@@ -3292,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.11346231222717</v>
+        <v>-0.140512690808377</v>
       </c>
     </row>
     <row r="209">
@@ -3303,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.360926085019391</v>
+        <v>-0.375163867072348</v>
       </c>
     </row>
     <row r="210">
@@ -3325,7 +3319,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.287852414423816</v>
+        <v>-0.241556760222225</v>
       </c>
     </row>
     <row r="212">
@@ -3336,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.231305790790333</v>
+        <v>-0.974697697960606</v>
       </c>
     </row>
     <row r="213">
@@ -3347,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.27065670073738</v>
+        <v>-0.318629464123336</v>
       </c>
     </row>
     <row r="214">
@@ -3358,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.310647756327657</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="215">
@@ -3402,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.219347796348945</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="219">
@@ -3413,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.264926580043296</v>
+        <v>-0.302660258404039</v>
       </c>
     </row>
     <row r="220">
@@ -3490,7 +3484,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.172438726901487</v>
+        <v>-0.0403556128520954</v>
       </c>
     </row>
     <row r="227">
@@ -3545,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0968534941224849</v>
+        <v>0.196680664927288</v>
       </c>
     </row>
     <row r="232">
@@ -3578,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.19936257876364</v>
+        <v>-0.232775679081211</v>
       </c>
     </row>
     <row r="235">
@@ -3589,7 +3583,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.381144310387531</v>
       </c>
     </row>
     <row r="236">
@@ -3611,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.160829825343367</v>
       </c>
     </row>
     <row r="238">
@@ -3655,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.198821005909372</v>
+        <v>-0.212005549632644</v>
       </c>
     </row>
     <row r="242">
@@ -3699,7 +3693,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.227569958183394</v>
       </c>
     </row>
     <row r="246">
@@ -3710,7 +3704,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.0893677837581974</v>
+        <v>-0.150379324435122</v>
       </c>
     </row>
     <row r="247">
@@ -3721,7 +3715,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.244924689203808</v>
+        <v>-0.156023171959989</v>
       </c>
     </row>
     <row r="248">
@@ -3732,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.221046314685488</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="249">
@@ -3743,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.397660069423042</v>
+        <v>-0.333067817034937</v>
       </c>
     </row>
     <row r="250">
@@ -3765,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.366390879005471</v>
+        <v>-0.318654385255388</v>
       </c>
     </row>
     <row r="252">
@@ -3798,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.231254994960718</v>
+        <v>-0.17052448362169</v>
       </c>
     </row>
     <row r="255">
@@ -3842,7 +3836,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.150421128282299</v>
       </c>
     </row>
     <row r="259">
@@ -3853,7 +3847,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.189055385474365</v>
+        <v>-0.201525274164183</v>
       </c>
     </row>
     <row r="260">
@@ -3864,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.174179590729596</v>
+        <v>-0.162667606053399</v>
       </c>
     </row>
     <row r="261">
@@ -3908,7 +3902,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.451030843010319</v>
+        <v>-0.330566371768815</v>
       </c>
     </row>
     <row r="265">
@@ -3919,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.387269620668146</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="266">
@@ -3930,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.34691366847669</v>
+        <v>-0.231871363707006</v>
       </c>
     </row>
     <row r="267">
@@ -3941,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.281513259702514</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="268">
@@ -3952,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.213121794411159</v>
+        <v>-0.246879152463047</v>
       </c>
     </row>
     <row r="269">
@@ -3974,7 +3968,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.34956928085663</v>
+        <v>-0.350060568678709</v>
       </c>
     </row>
     <row r="271">
@@ -4007,7 +4001,7 @@
         <v>16</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.362478669458939</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="274">
@@ -4018,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.154862725867355</v>
+        <v>-0.191749322482255</v>
       </c>
     </row>
     <row r="275">
@@ -4040,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.143449074793837</v>
+        <v>-0.194580881992753</v>
       </c>
     </row>
     <row r="277">
@@ -4095,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0919881962200979</v>
+        <v>0.342023445210515</v>
       </c>
     </row>
     <row r="282">
@@ -4106,7 +4100,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>0.102292827692012</v>
+        <v>-0.22824140764661</v>
       </c>
     </row>
     <row r="283">
@@ -4117,7 +4111,7 @@
         <v>16</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.161996178806001</v>
+        <v>-0.213829254070672</v>
       </c>
     </row>
     <row r="284">
@@ -4150,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.302143223267784</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="287">
@@ -4161,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.182017757161243</v>
+        <v>-0.216949705832045</v>
       </c>
     </row>
     <row r="288">
@@ -4205,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.673449590563434</v>
       </c>
     </row>
     <row r="292">
@@ -4216,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.18489894639923</v>
+        <v>-0.197118055900917</v>
       </c>
     </row>
     <row r="293">
@@ -4227,7 +4221,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.793219755850117</v>
+        <v>-0.541942376119765</v>
       </c>
     </row>
     <row r="294">
@@ -4249,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.14865948826134</v>
+        <v>-0.141308524427588</v>
       </c>
     </row>
     <row r="296">
@@ -4282,7 +4276,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.310572555934379</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="299">
@@ -4304,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.183165387902329</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="301">
@@ -4315,7 +4309,7 @@
         <v>16</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.623196093783788</v>
       </c>
     </row>
     <row r="302">
@@ -4326,7 +4320,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.260253485970884</v>
       </c>
     </row>
     <row r="303">
@@ -4337,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.414378840278783</v>
+        <v>-0.623251352873927</v>
       </c>
     </row>
     <row r="304">
@@ -4359,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.253713758661562</v>
+        <v>-0.127216788056199</v>
       </c>
     </row>
     <row r="306">
@@ -4370,7 +4364,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.10728391765248</v>
+        <v>0.0418792979373492</v>
       </c>
     </row>
     <row r="307">
@@ -4381,7 +4375,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.273083971006584</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="308">
@@ -4403,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.470997990334126</v>
+        <v>-1.25176432909666</v>
       </c>
     </row>
     <row r="310">
@@ -4436,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.152834985488817</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="313">
@@ -4447,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.195045962396469</v>
+        <v>-0.167714409976937</v>
       </c>
     </row>
     <row r="314">
@@ -4469,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.295846705157947</v>
+        <v>-0.488575815190097</v>
       </c>
     </row>
     <row r="316">
@@ -4546,7 +4540,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.217981681423734</v>
+        <v>-0.165969684602823</v>
       </c>
     </row>
     <row r="323">
@@ -4568,7 +4562,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.153679377336925</v>
       </c>
     </row>
     <row r="325">
@@ -4590,7 +4584,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.390654472393138</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="327">
@@ -4601,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.170791263362734</v>
+        <v>-0.174665168306098</v>
       </c>
     </row>
     <row r="328">
@@ -4645,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.527435408688939</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="332">
@@ -4656,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.179685102123985</v>
+        <v>-0.186343091009136</v>
       </c>
     </row>
     <row r="333">
@@ -4689,7 +4683,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.152465160638404</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="336">
@@ -4722,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.164897699069432</v>
+        <v>-0.0859424026608895</v>
       </c>
     </row>
     <row r="339">
@@ -4755,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.198345441108644</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="342">
@@ -4766,7 +4760,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.157164122372471</v>
+        <v>-0.148495068373753</v>
       </c>
     </row>
     <row r="343">
@@ -4777,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.324464005668837</v>
+        <v>-0.429416093931719</v>
       </c>
     </row>
     <row r="344">
@@ -4788,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>-0.180910007099315</v>
+        <v>-0.224166875782717</v>
       </c>
     </row>
     <row r="345">
@@ -4799,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>0.118377031099764</v>
+        <v>0.135793285618139</v>
       </c>
     </row>
     <row r="346">
@@ -4843,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.133208449839997</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="350">
@@ -4876,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.186102062876902</v>
       </c>
     </row>
     <row r="353">
@@ -4887,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.183545583266342</v>
+        <v>-0.224682839631263</v>
       </c>
     </row>
     <row r="354">
@@ -4920,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.157003320884841</v>
       </c>
     </row>
     <row r="357">
@@ -4931,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>0.00653273860508286</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="358">
@@ -4986,7 +4980,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.170517106616241</v>
+        <v>-0.118346969978418</v>
       </c>
     </row>
     <row r="363">
@@ -4997,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.230350928840138</v>
+        <v>-0.333819985919868</v>
       </c>
     </row>
     <row r="364">
@@ -5019,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.358468944071556</v>
+        <v>-0.275132042864208</v>
       </c>
     </row>
     <row r="366">
@@ -5052,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.186361512698932</v>
+        <v>-0.188793869235349</v>
       </c>
     </row>
     <row r="369">
@@ -5063,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.218139959458429</v>
+        <v>-0.318677354092091</v>
       </c>
     </row>
     <row r="370">
@@ -5085,7 +5079,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.297771681342389</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="372">
@@ -5239,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.168339790735534</v>
+        <v>-0.156535631547515</v>
       </c>
     </row>
     <row r="386">
@@ -5250,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.22673945110399</v>
       </c>
     </row>
     <row r="387">
@@ -5261,7 +5255,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.239770668507917</v>
       </c>
     </row>
     <row r="388">
@@ -5283,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.282703524778273</v>
+        <v>-0.463285140983885</v>
       </c>
     </row>
     <row r="390">
@@ -5305,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.213921574570662</v>
+        <v>0.0958517379827326</v>
       </c>
     </row>
     <row r="392">
@@ -5316,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.16916330427785</v>
+        <v>-0.247036883092318</v>
       </c>
     </row>
     <row r="393">
@@ -5327,7 +5321,7 @@
         <v>16</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.174581134646013</v>
+        <v>-0.221973333754488</v>
       </c>
     </row>
     <row r="394">
@@ -5338,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.253141822444853</v>
+        <v>-0.272751146810864</v>
       </c>
     </row>
     <row r="395">
@@ -5349,7 +5343,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.0856943030623696</v>
+        <v>-0.0443718496396324</v>
       </c>
     </row>
     <row r="396">
@@ -5360,7 +5354,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.184810852896387</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="397">
@@ -5393,7 +5387,7 @@
         <v>16</v>
       </c>
       <c r="C399" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.148541024056003</v>
       </c>
     </row>
     <row r="400">
@@ -5437,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-0.228660132820805</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="404">
@@ -5470,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.172983904485845</v>
+        <v>-0.168530447126776</v>
       </c>
     </row>
     <row r="407">
@@ -5492,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>0.156542288821613</v>
+        <v>0.129539413291078</v>
       </c>
     </row>
     <row r="409">
@@ -5503,7 +5497,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.166014089995866</v>
       </c>
     </row>
     <row r="410">
@@ -5525,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.333844825141955</v>
+        <v>-0.297609899190067</v>
       </c>
     </row>
     <row r="412">
@@ -5536,7 +5530,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.162157531121496</v>
       </c>
     </row>
     <row r="413">
@@ -5547,7 +5541,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.150555019363064</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="414">
@@ -5558,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.296985847907516</v>
+        <v>-0.201434306919612</v>
       </c>
     </row>
     <row r="415">
@@ -5569,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.161876348616237</v>
+        <v>-0.149052621195822</v>
       </c>
     </row>
     <row r="416">
@@ -5602,7 +5596,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.260677211808021</v>
+        <v>-0.334493248075334</v>
       </c>
     </row>
     <row r="419">
@@ -5613,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.102478846740323</v>
+        <v>-0.244423590315933</v>
       </c>
     </row>
     <row r="420">
@@ -5624,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-0.16620839141708</v>
+        <v>-0.213849030582248</v>
       </c>
     </row>
     <row r="421">
@@ -5635,7 +5629,7 @@
         <v>16</v>
       </c>
       <c r="C421" t="n">
-        <v>-0.386185035946424</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="422">
@@ -5690,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.213226490021738</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="427">
@@ -5745,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>0.0228366267102738</v>
+        <v>0.0681887763103938</v>
       </c>
     </row>
     <row r="432">
@@ -5789,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.172164326562371</v>
+        <v>-0.188687789646268</v>
       </c>
     </row>
     <row r="436">
@@ -5811,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.194327984367116</v>
       </c>
     </row>
     <row r="438">
@@ -5855,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.120170448684577</v>
+        <v>-0.110908976372984</v>
       </c>
     </row>
     <row r="442">
@@ -5899,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.199300039404865</v>
       </c>
     </row>
     <row r="446">
@@ -5921,7 +5915,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.135664576581847</v>
+        <v>-0.083009739285633</v>
       </c>
     </row>
     <row r="448">
@@ -5932,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.229158697405115</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="449">
@@ -5943,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.400437591404231</v>
+        <v>-0.343361162867608</v>
       </c>
     </row>
     <row r="450">
@@ -5987,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.223920550637475</v>
       </c>
     </row>
     <row r="454">
@@ -5998,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.370857359196232</v>
+        <v>-0.260547634173175</v>
       </c>
     </row>
     <row r="455">
@@ -6009,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.179333960063693</v>
       </c>
     </row>
     <row r="456">
@@ -6042,7 +6036,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.151570453764158</v>
+        <v>-0.154232245298644</v>
       </c>
     </row>
     <row r="459">
@@ -6053,7 +6047,7 @@
         <v>16</v>
       </c>
       <c r="C459" t="n">
-        <v>-0.156528422421877</v>
+        <v>-0.155039756532857</v>
       </c>
     </row>
     <row r="460">
@@ -6064,7 +6058,7 @@
         <v>16</v>
       </c>
       <c r="C460" t="n">
-        <v>-0.352003045541374</v>
+        <v>-0.246034208540593</v>
       </c>
     </row>
     <row r="461">
@@ -6097,7 +6091,7 @@
         <v>16</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.166678196116051</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="464">
@@ -6108,7 +6102,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.575002279769222</v>
+        <v>-0.405217080456169</v>
       </c>
     </row>
     <row r="465">
@@ -6130,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.430814526085086</v>
+        <v>-0.34389715857559</v>
       </c>
     </row>
     <row r="467">
@@ -6141,7 +6135,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.333172782142859</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="468">
@@ -6152,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.188484955657576</v>
+        <v>-0.162554778913176</v>
       </c>
     </row>
     <row r="469">
@@ -6196,7 +6190,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.155852656399333</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="473">
@@ -6207,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.175234593728878</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="474">
@@ -6240,7 +6234,7 @@
         <v>16</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.157710913373977</v>
+        <v>-0.167726550446015</v>
       </c>
     </row>
     <row r="477">
@@ -6295,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>0.112835132778171</v>
+        <v>0.225971817382489</v>
       </c>
     </row>
     <row r="482">
@@ -6306,7 +6300,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.116671275323644</v>
+        <v>-0.391712437569014</v>
       </c>
     </row>
     <row r="483">
@@ -6317,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.121474379279053</v>
+        <v>-0.119362228569384</v>
       </c>
     </row>
     <row r="484">
@@ -6350,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.364174398638594</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="487">
@@ -6394,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.320291315139007</v>
       </c>
     </row>
     <row r="491">
@@ -6427,7 +6421,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.472812784819036</v>
+        <v>-0.330667831780318</v>
       </c>
     </row>
     <row r="494">
@@ -6449,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.146456656983234</v>
+        <v>-0.153467978735649</v>
       </c>
     </row>
     <row r="496">
@@ -6482,7 +6476,7 @@
         <v>16</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.309391176941759</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="499">
@@ -6504,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.20314190195692</v>
+        <v>-0.176652993563524</v>
       </c>
     </row>
     <row r="501">
@@ -6526,7 +6520,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.219168680069988</v>
       </c>
     </row>
     <row r="503">
@@ -6537,7 +6531,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.701168288932275</v>
+        <v>-0.70010223209198</v>
       </c>
     </row>
     <row r="504">
@@ -6559,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="C505" t="n">
-        <v>-0.00780804872696694</v>
+        <v>0.0803510393935074</v>
       </c>
     </row>
     <row r="506">
@@ -6570,7 +6564,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.046375085478418</v>
+        <v>-0.166953965441211</v>
       </c>
     </row>
     <row r="507">
@@ -6603,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.540978757539315</v>
+        <v>-1.66740819389009</v>
       </c>
     </row>
     <row r="510">
@@ -6636,7 +6630,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.177954477239312</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="513">
@@ -6647,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.190661266187381</v>
+        <v>-0.198893689335339</v>
       </c>
     </row>
     <row r="514">
@@ -6669,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.144443567249629</v>
+        <v>-1.14606484298802</v>
       </c>
     </row>
     <row r="516">
@@ -6691,7 +6685,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.217847281940567</v>
+        <v>-0.179273363010211</v>
       </c>
     </row>
     <row r="518">
@@ -6702,7 +6696,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.155456155384956</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="519">
@@ -6746,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.279188245143901</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="523">
@@ -6768,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.155842040926187</v>
       </c>
     </row>
     <row r="525">
@@ -6867,7 +6861,7 @@
         <v>16</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.169617736223691</v>
       </c>
     </row>
     <row r="534">
@@ -6922,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.1903463666079</v>
+        <v>-0.0990297797287394</v>
       </c>
     </row>
     <row r="539">
@@ -6955,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.197380213764179</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="542">
@@ -6966,7 +6960,7 @@
         <v>16</v>
       </c>
       <c r="C542" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.153708136609261</v>
       </c>
     </row>
     <row r="543">
@@ -6988,7 +6982,7 @@
         <v>16</v>
       </c>
       <c r="C544" t="n">
-        <v>-0.152644475810048</v>
+        <v>-0.134891759956188</v>
       </c>
     </row>
     <row r="545">
@@ -6999,7 +6993,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>0.132106126049034</v>
+        <v>0.114420703801692</v>
       </c>
     </row>
     <row r="546">
@@ -7043,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.153113267292251</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="550">
@@ -7076,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.29922838505913</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="553">
@@ -7087,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.15916804178326</v>
+        <v>-0.213040247923009</v>
       </c>
     </row>
     <row r="554">
@@ -7098,7 +7092,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.161738132802427</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="555">
@@ -7120,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.440806638500944</v>
+        <v>-0.384720549162924</v>
       </c>
     </row>
     <row r="557">
@@ -7131,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.0692378474952902</v>
+        <v>-0.189898946935556</v>
       </c>
     </row>
     <row r="558">
@@ -7186,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.183951818939431</v>
+        <v>-0.143019866351219</v>
       </c>
     </row>
     <row r="563">
@@ -7197,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.225053493713732</v>
+        <v>-0.319054520352438</v>
       </c>
     </row>
     <row r="564">
@@ -7219,7 +7213,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.518525155936704</v>
+        <v>-0.252047104741798</v>
       </c>
     </row>
     <row r="566">
@@ -7252,7 +7246,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.180661813725336</v>
+        <v>-0.179064637243619</v>
       </c>
     </row>
     <row r="569">
@@ -7263,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.246885799042204</v>
+        <v>-0.209755712452471</v>
       </c>
     </row>
     <row r="570">
@@ -7274,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.430548745654304</v>
       </c>
     </row>
     <row r="571">
@@ -7285,7 +7279,7 @@
         <v>16</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.203983550813772</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="572">
@@ -7406,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.171656171471237</v>
       </c>
     </row>
     <row r="583">
@@ -7461,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.20380889556936</v>
+        <v>-0.300548959163042</v>
       </c>
     </row>
     <row r="588">
@@ -7472,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.161827431115854</v>
+        <v>-0.14906204865899</v>
       </c>
     </row>
     <row r="589">
@@ -7483,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.139667101172047</v>
+        <v>-0.15068643217228</v>
       </c>
     </row>
     <row r="590">
@@ -7505,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.276841031795697</v>
+        <v>-0.221572815648381</v>
       </c>
     </row>
     <row r="592">
@@ -7516,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.76905793509512</v>
+        <v>-0.745202269667438</v>
       </c>
     </row>
     <row r="593">
@@ -7527,7 +7521,7 @@
         <v>16</v>
       </c>
       <c r="C593" t="n">
-        <v>-0.230681709115874</v>
+        <v>-0.284130156955557</v>
       </c>
     </row>
     <row r="594">
@@ -7538,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.337057493287994</v>
+        <v>-0.322133483027087</v>
       </c>
     </row>
     <row r="595">
@@ -7549,7 +7543,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.0738807907589978</v>
+        <v>0.14544068815447</v>
       </c>
     </row>
     <row r="596">
@@ -7593,7 +7587,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.194467072861997</v>
       </c>
     </row>
     <row r="600">
@@ -7626,7 +7620,7 @@
         <v>16</v>
       </c>
       <c r="C602" t="n">
-        <v>0.0447896998758497</v>
+        <v>-0.117490525176212</v>
       </c>
     </row>
     <row r="603">
@@ -7681,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.22087843653367</v>
+        <v>-0.156636893711014</v>
       </c>
     </row>
     <row r="608">
@@ -7703,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="C609" t="n">
-        <v>-0.101472086943162</v>
+        <v>-0.14899677126969</v>
       </c>
     </row>
     <row r="610">
@@ -7725,7 +7719,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.157032895361689</v>
+        <v>-0.152589687882668</v>
       </c>
     </row>
     <row r="612">
@@ -7758,7 +7752,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.173412557439089</v>
+        <v>-0.165614659230747</v>
       </c>
     </row>
     <row r="615">
@@ -7780,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.191475409664143</v>
       </c>
     </row>
     <row r="617">
@@ -7868,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.150232402407459</v>
+        <v>-0.15922146675477</v>
       </c>
     </row>
     <row r="625">
@@ -7890,7 +7884,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.141204574768355</v>
       </c>
     </row>
     <row r="627">
@@ -7901,7 +7895,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.807156915167814</v>
+        <v>-0.676576586462812</v>
       </c>
     </row>
     <row r="628">
@@ -7912,7 +7906,7 @@
         <v>16</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.275190286963924</v>
       </c>
     </row>
     <row r="629">
@@ -7923,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.320713762722783</v>
       </c>
     </row>
     <row r="630">
@@ -7956,7 +7950,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.255204420209752</v>
+        <v>-0.591797271406796</v>
       </c>
     </row>
     <row r="633">
@@ -7978,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.150096372381584</v>
+        <v>-0.136825305976706</v>
       </c>
     </row>
     <row r="635">
@@ -8000,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.199888703955994</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="637">
@@ -8011,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.295555198627767</v>
+        <v>-0.54566779384098</v>
       </c>
     </row>
     <row r="638">
@@ -8022,7 +8016,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.1754830656827</v>
+        <v>-0.190915641294125</v>
       </c>
     </row>
     <row r="639">
@@ -8132,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.290868913483258</v>
+        <v>-0.166746473192219</v>
       </c>
     </row>
     <row r="649">
@@ -8143,7 +8137,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>0.0180429736989347</v>
+        <v>0.0596399187103737</v>
       </c>
     </row>
     <row r="650">
@@ -8154,7 +8148,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.163662491323853</v>
       </c>
     </row>
     <row r="651">
@@ -8187,7 +8181,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.260702450900152</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="654">
@@ -8220,7 +8214,7 @@
         <v>16</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.466415796301349</v>
+        <v>-0.330763277962957</v>
       </c>
     </row>
     <row r="657">
@@ -8253,7 +8247,7 @@
         <v>16</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.153538625813445</v>
+        <v>-0.215940956980416</v>
       </c>
     </row>
     <row r="660">
@@ -8275,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.292817062685428</v>
+        <v>-0.186587277718228</v>
       </c>
     </row>
     <row r="662">
@@ -8286,7 +8280,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.283077810365868</v>
+        <v>-0.323392586162573</v>
       </c>
     </row>
     <row r="663">
@@ -8297,7 +8291,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.144242174645271</v>
+        <v>-0.140046480976329</v>
       </c>
     </row>
     <row r="664">
@@ -8341,7 +8335,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.424535059390396</v>
+        <v>-0.326191057203198</v>
       </c>
     </row>
     <row r="668">
@@ -8363,7 +8357,7 @@
         <v>16</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.21888503363311</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="670">
@@ -8396,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.222083273037859</v>
+        <v>-0.178225494917317</v>
       </c>
     </row>
     <row r="673">
@@ -8440,7 +8434,7 @@
         <v>16</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.150780060755469</v>
       </c>
     </row>
     <row r="677">
@@ -8451,7 +8445,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.217117757792745</v>
+        <v>-0.149710315017931</v>
       </c>
     </row>
     <row r="678">
@@ -8495,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.259808428817174</v>
+        <v>-0.25201789604615</v>
       </c>
     </row>
     <row r="682">
@@ -8506,7 +8500,7 @@
         <v>16</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.16720829562409</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="683">
@@ -8528,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.17974681562342</v>
+        <v>-0.20396797405981</v>
       </c>
     </row>
     <row r="685">
@@ -8539,7 +8533,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.279995432259484</v>
       </c>
     </row>
     <row r="686">
@@ -8550,7 +8544,7 @@
         <v>16</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.204145070495966</v>
+        <v>-0.224723264555956</v>
       </c>
     </row>
     <row r="687">
@@ -8561,7 +8555,7 @@
         <v>16</v>
       </c>
       <c r="C687" t="n">
-        <v>-0.145331474899615</v>
+        <v>-0.150349296103859</v>
       </c>
     </row>
     <row r="688">
@@ -8572,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.360033340710166</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="689">
@@ -8594,7 +8588,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.181179445927486</v>
+        <v>-0.227438092340708</v>
       </c>
     </row>
     <row r="691">
@@ -8605,7 +8599,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.287921382663596</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="692">
@@ -8616,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.130498326414237</v>
+        <v>-0.222301233716047</v>
       </c>
     </row>
     <row r="693">
@@ -8660,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.143751238613997</v>
+        <v>-0.147423107232511</v>
       </c>
     </row>
     <row r="697">
@@ -8682,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.142619526021732</v>
+        <v>-0.130194935660611</v>
       </c>
     </row>
     <row r="699">
@@ -8693,7 +8687,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.181967163513798</v>
+        <v>-0.169409793740764</v>
       </c>
     </row>
     <row r="700">
@@ -8726,7 +8720,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.152609049763008</v>
+        <v>-0.185562985492588</v>
       </c>
     </row>
     <row r="703">
@@ -8759,7 +8753,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.525527798158871</v>
+        <v>-0.470312532151492</v>
       </c>
     </row>
     <row r="706">
@@ -8770,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.623737714369555</v>
       </c>
     </row>
     <row r="707">
@@ -8781,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.197339215717472</v>
+        <v>-0.179108587279785</v>
       </c>
     </row>
     <row r="708">
@@ -8792,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.149566031622603</v>
       </c>
     </row>
     <row r="709">
@@ -8803,7 +8797,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.34841306721225</v>
+        <v>-0.542230954945093</v>
       </c>
     </row>
     <row r="710">
@@ -8814,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.403054789976076</v>
+        <v>-0.21828542987418</v>
       </c>
     </row>
     <row r="711">
@@ -8825,7 +8819,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.137460511584796</v>
       </c>
     </row>
     <row r="712">
@@ -8902,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.261550272872217</v>
+        <v>-0.416120200455014</v>
       </c>
     </row>
     <row r="719">
@@ -8924,7 +8918,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.247908576891181</v>
+        <v>-0.461998904795756</v>
       </c>
     </row>
     <row r="721">
@@ -8935,7 +8929,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.138445834348157</v>
+        <v>-0.177667876684995</v>
       </c>
     </row>
     <row r="722">
@@ -8946,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.381692565375031</v>
+        <v>-0.463557723334785</v>
       </c>
     </row>
     <row r="723">
@@ -8979,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.326771044760089</v>
+        <v>-0.218041718697861</v>
       </c>
     </row>
     <row r="726">
@@ -8990,7 +8984,7 @@
         <v>16</v>
       </c>
       <c r="C726" t="n">
-        <v>-0.254010560627414</v>
+        <v>-0.240844939495978</v>
       </c>
     </row>
     <row r="727">
@@ -9012,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.364114506196886</v>
+        <v>-0.571398929968366</v>
       </c>
     </row>
     <row r="729">
@@ -9023,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.170014983044396</v>
       </c>
     </row>
     <row r="730">
@@ -9034,7 +9028,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>0.485088389205367</v>
+        <v>-0.272793273467145</v>
       </c>
     </row>
     <row r="731">
@@ -9056,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.215186385230576</v>
       </c>
     </row>
     <row r="733">
@@ -9089,7 +9083,7 @@
         <v>16</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.301864992853377</v>
+        <v>-0.356089636377416</v>
       </c>
     </row>
     <row r="736">
@@ -9199,7 +9193,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.29773121258216</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="746">
@@ -9210,7 +9204,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.24471636606549</v>
+        <v>-0.296949783642787</v>
       </c>
     </row>
     <row r="747">
@@ -9232,7 +9226,7 @@
         <v>16</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.211094404864494</v>
       </c>
     </row>
     <row r="749">
@@ -9265,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.574252847980243</v>
+        <v>-0.389855484208266</v>
       </c>
     </row>
     <row r="752">
@@ -9276,7 +9270,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.255716408021862</v>
+        <v>-0.522872289881283</v>
       </c>
     </row>
     <row r="753">
@@ -9320,7 +9314,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.173588318136112</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="757">
@@ -9331,7 +9325,7 @@
         <v>16</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.183790535942574</v>
+        <v>-0.307722346997983</v>
       </c>
     </row>
     <row r="758">
@@ -9353,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.195721825299999</v>
       </c>
     </row>
     <row r="760">
@@ -9386,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.298862704115866</v>
+        <v>-0.251540875963045</v>
       </c>
     </row>
     <row r="763">
@@ -9397,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.0986243320159108</v>
+        <v>0.0250073126710659</v>
       </c>
     </row>
     <row r="764">
@@ -9430,7 +9424,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.332447063443331</v>
+        <v>-0.37394931899831</v>
       </c>
     </row>
     <row r="767">
@@ -9441,7 +9435,7 @@
         <v>16</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.14115544135285</v>
+        <v>-0.104705451638959</v>
       </c>
     </row>
     <row r="768">
@@ -9452,7 +9446,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.10129129160635</v>
+        <v>-0.119757747677144</v>
       </c>
     </row>
     <row r="769">
@@ -9463,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.232829372108794</v>
+        <v>-0.217687598563704</v>
       </c>
     </row>
     <row r="770">
@@ -9496,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.206588895173217</v>
+        <v>-0.262047697827332</v>
       </c>
     </row>
     <row r="773">
@@ -9507,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.238447789933082</v>
+        <v>-0.248985691768505</v>
       </c>
     </row>
     <row r="774">
@@ -9540,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.225250899613077</v>
+        <v>-0.410440840210858</v>
       </c>
     </row>
     <row r="777">
@@ -9573,7 +9567,7 @@
         <v>16</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.112836056161575</v>
+        <v>-0.106638584468474</v>
       </c>
     </row>
     <row r="780">
@@ -9584,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.290846829875733</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="781">
@@ -9595,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.147972174683789</v>
       </c>
     </row>
     <row r="782">
@@ -9628,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.19328140924963</v>
+        <v>-0.184361623466345</v>
       </c>
     </row>
     <row r="785">
@@ -9639,7 +9633,7 @@
         <v>16</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.274932299652768</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="786">
@@ -9650,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.141246232987916</v>
+        <v>-0.148395283914021</v>
       </c>
     </row>
     <row r="787">
@@ -9661,7 +9655,7 @@
         <v>16</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.392770169252212</v>
+        <v>-0.220256952162842</v>
       </c>
     </row>
     <row r="788">
@@ -9672,7 +9666,7 @@
         <v>16</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.143423998138547</v>
+        <v>-0.149520128983584</v>
       </c>
     </row>
     <row r="789">
@@ -9683,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.16069842576988</v>
+        <v>-0.184991873507887</v>
       </c>
     </row>
     <row r="790">
@@ -9716,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.136654528409026</v>
       </c>
     </row>
     <row r="793">
@@ -9727,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.890696036738966</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="794">
@@ -9738,7 +9732,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.778286994564745</v>
       </c>
     </row>
     <row r="795">
@@ -9749,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.32784695478341</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="796">
@@ -9815,7 +9809,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.151221810220636</v>
+        <v>-0.103504488718193</v>
       </c>
     </row>
     <row r="802">
@@ -9848,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.169795216450214</v>
+        <v>-0.157553712514592</v>
       </c>
     </row>
     <row r="805">
@@ -9881,7 +9875,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.289059543562591</v>
       </c>
     </row>
     <row r="808">
@@ -9892,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>0.257874477777834</v>
+        <v>0.413461549216258</v>
       </c>
     </row>
     <row r="809">
@@ -9903,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.217845103426971</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="810">
@@ -9925,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.165640240856946</v>
+        <v>-0.157028966686143</v>
       </c>
     </row>
     <row r="812">
@@ -9936,7 +9930,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.153698460735606</v>
+        <v>-0.0286209211739794</v>
       </c>
     </row>
     <row r="813">
@@ -9958,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.319586413947672</v>
+        <v>-0.885605245089759</v>
       </c>
     </row>
     <row r="815">
@@ -9980,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.129718369534771</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="817">
@@ -10013,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.219728843114444</v>
+        <v>-0.182202733413792</v>
       </c>
     </row>
     <row r="820">
@@ -10024,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>0.102853466832281</v>
+        <v>0.11723924865498</v>
       </c>
     </row>
     <row r="821">
@@ -10035,7 +10029,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.403412783958689</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="822">
@@ -10046,7 +10040,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.149899841504105</v>
+        <v>-0.154290081731273</v>
       </c>
     </row>
     <row r="823">
@@ -10112,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.366542803844826</v>
+        <v>-0.412185436219026</v>
       </c>
     </row>
     <row r="829">
@@ -10123,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.258563501948542</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="830">
@@ -10134,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.150435621791938</v>
+        <v>-0.149786778286938</v>
       </c>
     </row>
     <row r="831">
@@ -10167,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>0.0113889349732043</v>
+        <v>-0.548714023189683</v>
       </c>
     </row>
     <row r="834">
@@ -10200,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.193252189227542</v>
+        <v>-0.174709509906239</v>
       </c>
     </row>
     <row r="837">
@@ -10233,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.152098400494961</v>
       </c>
     </row>
     <row r="840">
@@ -10277,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.154152730507766</v>
+        <v>-0.181804643679726</v>
       </c>
     </row>
     <row r="844">
@@ -10288,7 +10282,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.179327062541618</v>
+        <v>-0.572421806205173</v>
       </c>
     </row>
     <row r="845">
@@ -10310,7 +10304,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.256481768655668</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="847">
@@ -10321,7 +10315,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.309759806961443</v>
+        <v>-0.265843026951501</v>
       </c>
     </row>
     <row r="848">
@@ -10343,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.157683088400075</v>
+        <v>-0.285942400916156</v>
       </c>
     </row>
     <row r="850">
@@ -10365,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.18538856244542</v>
+        <v>0.0718776080317465</v>
       </c>
     </row>
     <row r="852">
@@ -10376,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.364959648532816</v>
       </c>
     </row>
     <row r="853">
@@ -10398,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.441248993915138</v>
+        <v>-0.603716905227829</v>
       </c>
     </row>
     <row r="855">
@@ -10409,7 +10403,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.210482190076634</v>
+        <v>-0.161256487268096</v>
       </c>
     </row>
     <row r="856">
@@ -10431,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.153831280349745</v>
+        <v>-0.161858739234149</v>
       </c>
     </row>
     <row r="858">
@@ -10453,7 +10447,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.240205787641304</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="860">
@@ -10475,7 +10469,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.238442777330996</v>
       </c>
     </row>
     <row r="862">
@@ -10508,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.233343195416931</v>
       </c>
     </row>
     <row r="865">
@@ -10541,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>0.328164771378774</v>
+        <v>0.513120041182169</v>
       </c>
     </row>
     <row r="868">
@@ -10552,7 +10546,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.462707037609916</v>
+        <v>0.238706847808669</v>
       </c>
     </row>
     <row r="869">
@@ -10563,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.459566738980225</v>
+        <v>-0.173796750054567</v>
       </c>
     </row>
     <row r="870">
@@ -10574,7 +10568,7 @@
         <v>16</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.222892728771535</v>
       </c>
     </row>
     <row r="871">
@@ -10629,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.380932915797619</v>
+        <v>-0.540046518087331</v>
       </c>
     </row>
     <row r="876">
@@ -10662,7 +10656,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.176537177733348</v>
       </c>
     </row>
     <row r="879">
@@ -10673,7 +10667,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.148798000616149</v>
+        <v>-0.152613055356188</v>
       </c>
     </row>
     <row r="880">
@@ -10684,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.203009067705879</v>
+        <v>-0.201402897230812</v>
       </c>
     </row>
     <row r="881">
@@ -10695,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.174283268545837</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="882">
@@ -10728,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.151603922919442</v>
+        <v>-0.188011098798058</v>
       </c>
     </row>
     <row r="885">
@@ -10750,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.42215704960896</v>
+        <v>-0.171281335707214</v>
       </c>
     </row>
     <row r="887">
@@ -10761,7 +10755,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.469346075735897</v>
       </c>
     </row>
     <row r="888">
@@ -10772,7 +10766,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.10706740592461</v>
+        <v>-0.15750639938632</v>
       </c>
     </row>
     <row r="889">
@@ -10805,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.245850377561471</v>
+        <v>-0.329597499300903</v>
       </c>
     </row>
     <row r="892">
@@ -10827,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.305917914075571</v>
+        <v>-0.24609650951463</v>
       </c>
     </row>
     <row r="894">
@@ -10838,7 +10832,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.150672747062208</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="895">
@@ -10849,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.229144761100205</v>
+        <v>-0.26381972540363</v>
       </c>
     </row>
     <row r="896">
@@ -10860,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.251497434012685</v>
       </c>
     </row>
     <row r="897">
@@ -10893,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.292638421936257</v>
+        <v>-0.210414560418767</v>
       </c>
     </row>
     <row r="900">
@@ -10926,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.187566740724828</v>
       </c>
     </row>
     <row r="903">
@@ -10948,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.0768204577438749</v>
+        <v>0.160818576604865</v>
       </c>
     </row>
     <row r="905">
@@ -10970,7 +10964,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.196817975618138</v>
+        <v>-0.233133298175936</v>
       </c>
     </row>
     <row r="907">
@@ -11025,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.200295368732955</v>
+        <v>-0.207794097924985</v>
       </c>
     </row>
     <row r="912">
@@ -11036,7 +11030,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.171388561645273</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="913">
@@ -11047,7 +11041,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.245483736145798</v>
+        <v>-0.293696354444996</v>
       </c>
     </row>
     <row r="914">
@@ -11058,7 +11052,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.616993325043127</v>
+        <v>-0.629574824009965</v>
       </c>
     </row>
     <row r="915">
@@ -11069,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.165027187199804</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="916">
@@ -11080,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.694717695994118</v>
+        <v>-0.540697316130554</v>
       </c>
     </row>
     <row r="917">
@@ -11091,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.91196334857271</v>
+        <v>-0.208425952789737</v>
       </c>
     </row>
     <row r="918">
@@ -11102,7 +11096,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.461470957282244</v>
+        <v>-0.626972043918148</v>
       </c>
     </row>
     <row r="919">
@@ -11113,7 +11107,7 @@
         <v>16</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.425601130998765</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="920">
@@ -11146,7 +11140,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.370571469330932</v>
+        <v>-0.423641134453611</v>
       </c>
     </row>
     <row r="923">
@@ -11179,7 +11173,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.148529264657382</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="926">
@@ -11201,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.211454458174076</v>
+        <v>-0.229292195659223</v>
       </c>
     </row>
     <row r="928">
@@ -11212,7 +11206,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.182504840811292</v>
+        <v>-0.219269391781595</v>
       </c>
     </row>
     <row r="929">
@@ -11245,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>0.51426733403124</v>
+        <v>0.0505004901492998</v>
       </c>
     </row>
     <row r="932">
@@ -11267,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.161224186753444</v>
+        <v>-0.141252883620768</v>
       </c>
     </row>
     <row r="934">
@@ -11300,7 +11294,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.195806166319997</v>
+        <v>0.0396146004588426</v>
       </c>
     </row>
     <row r="937">
@@ -11311,7 +11305,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.155388643592227</v>
       </c>
     </row>
     <row r="938">
@@ -11322,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.141712150004338</v>
+        <v>-0.201949952246484</v>
       </c>
     </row>
     <row r="939">
@@ -11344,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.273122765742332</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="941">
@@ -11355,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.143406164734268</v>
+        <v>-0.079413611622889</v>
       </c>
     </row>
     <row r="942">
@@ -11366,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.148874623344006</v>
+        <v>-0.16167321604186</v>
       </c>
     </row>
     <row r="943">
@@ -11388,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.160238337544382</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="945">
@@ -11399,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.179418870623653</v>
       </c>
     </row>
     <row r="946">
@@ -11432,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.248920332040811</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="949">
@@ -11465,7 +11459,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>0.0577806114828141</v>
+        <v>0.0707197932384914</v>
       </c>
     </row>
     <row r="952">
@@ -11487,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.208924658235782</v>
+        <v>-0.193052883838188</v>
       </c>
     </row>
     <row r="954">
@@ -11509,7 +11503,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.431662902238317</v>
+        <v>-0.430412390589089</v>
       </c>
     </row>
     <row r="956">
@@ -11520,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.322234720407202</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="957">
@@ -11542,7 +11536,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.175908683150308</v>
+        <v>-0.169813652484274</v>
       </c>
     </row>
     <row r="959">
@@ -11553,7 +11547,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.143528398346049</v>
+        <v>-0.260340988378702</v>
       </c>
     </row>
     <row r="960">
@@ -11564,7 +11558,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.168495927103286</v>
       </c>
     </row>
     <row r="961">
@@ -11586,7 +11580,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.371962334345197</v>
+        <v>-0.411114106089306</v>
       </c>
     </row>
     <row r="963">
@@ -11597,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.146615246616537</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="964">
@@ -11608,7 +11602,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.188793252956823</v>
       </c>
     </row>
     <row r="965">
@@ -11619,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.355303371639397</v>
+        <v>-0.287244923421622</v>
       </c>
     </row>
     <row r="966">
@@ -11641,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.128137195376726</v>
+        <v>-0.128399316775717</v>
       </c>
     </row>
     <row r="968">
@@ -11674,7 +11668,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.182723961086154</v>
       </c>
     </row>
     <row r="971">
@@ -11685,7 +11679,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.165777477808201</v>
+        <v>-0.17943710971848</v>
       </c>
     </row>
     <row r="972">
@@ -11718,7 +11712,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.210759278584645</v>
+        <v>-0.210459824704555</v>
       </c>
     </row>
     <row r="975">
@@ -11751,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.201637054136605</v>
+        <v>-0.299211616774181</v>
       </c>
     </row>
     <row r="978">
@@ -11762,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.188193492725789</v>
+        <v>-0.153700843902711</v>
       </c>
     </row>
     <row r="979">
@@ -11784,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.151058226477126</v>
       </c>
     </row>
     <row r="981">
@@ -11795,7 +11789,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.00792919401990377</v>
+        <v>-0.0789840438925509</v>
       </c>
     </row>
     <row r="982">
@@ -11839,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.26637274857312</v>
+        <v>-0.295269148524057</v>
       </c>
     </row>
     <row r="986">
@@ -11850,7 +11844,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.155462646188506</v>
+        <v>-0.214720316858036</v>
       </c>
     </row>
     <row r="987">
@@ -11861,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.247050455459041</v>
       </c>
     </row>
     <row r="988">
@@ -11872,7 +11866,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>0.105007669433332</v>
+        <v>0.111378554256794</v>
       </c>
     </row>
     <row r="989">
@@ -11894,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.00589900531642384</v>
+        <v>0.062221798278436</v>
       </c>
     </row>
     <row r="991">
@@ -11905,7 +11899,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.314094006153991</v>
+        <v>-0.334674930659557</v>
       </c>
     </row>
     <row r="992">
@@ -11916,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.532356500000565</v>
+        <v>-0.846774056837142</v>
       </c>
     </row>
     <row r="993">
@@ -11927,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.273129364408128</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="994">
@@ -11949,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.165432618520837</v>
+        <v>-0.162195988018579</v>
       </c>
     </row>
     <row r="996">
@@ -11960,7 +11954,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.209213291280473</v>
+        <v>-0.204405802563449</v>
       </c>
     </row>
     <row r="997">
@@ -11971,7 +11965,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.151875740286186</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="998">
@@ -11993,7 +11987,7 @@
         <v>16</v>
       </c>
       <c r="C999" t="n">
-        <v>-1.14749439241382</v>
+        <v>-0.200277678314344</v>
       </c>
     </row>
     <row r="1000">
@@ -12026,7 +12020,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.494142775048978</v>
       </c>
     </row>
     <row r="1003">
@@ -12059,7 +12053,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.165932792842233</v>
       </c>
     </row>
     <row r="1006">
@@ -12070,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.199454937385466</v>
       </c>
     </row>
     <row r="1007">
@@ -12081,7 +12075,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.07626775297541</v>
       </c>
     </row>
     <row r="1008">
@@ -12125,7 +12119,7 @@
         <v>16</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.151514298228947</v>
       </c>
     </row>
     <row r="1012">
@@ -12147,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169565719592187</v>
       </c>
     </row>
     <row r="1014">
@@ -12158,7 +12152,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.163868092202907</v>
+        <v>-0.059728627994569</v>
       </c>
     </row>
     <row r="1015">
@@ -12224,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.237864238146082</v>
       </c>
     </row>
     <row r="1021">
@@ -12235,7 +12229,7 @@
         <v>16</v>
       </c>
       <c r="C1021" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.601501062967156</v>
       </c>
     </row>
     <row r="1022">
@@ -12257,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.154574966411206</v>
       </c>
     </row>
     <row r="1024">
@@ -12268,7 +12262,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.2355369524573</v>
       </c>
     </row>
     <row r="1025">
@@ -12356,7 +12350,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.186845681944154</v>
       </c>
     </row>
     <row r="1033">
@@ -12367,7 +12361,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.177485973729113</v>
       </c>
     </row>
     <row r="1034">
@@ -12378,7 +12372,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.159763313609467</v>
+        <v>-3.24700072466453</v>
       </c>
     </row>
     <row r="1035">
@@ -12400,7 +12394,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.279494860211061</v>
       </c>
     </row>
     <row r="1037">
@@ -12411,7 +12405,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161274499464736</v>
       </c>
     </row>
     <row r="1038">
@@ -12455,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.173994649703461</v>
       </c>
     </row>
     <row r="1042">
@@ -12466,7 +12460,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.159257821186685</v>
+        <v>-0.136348701038567</v>
       </c>
     </row>
     <row r="1043">
@@ -12477,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.671347082329064</v>
       </c>
     </row>
     <row r="1044">
@@ -12554,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.165544112296659</v>
       </c>
     </row>
     <row r="1051">
@@ -12587,7 +12581,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0437843678546062</v>
       </c>
     </row>
     <row r="1054">
@@ -12653,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.159622423065767</v>
+        <v>-0.139330926636303</v>
       </c>
     </row>
     <row r="1060">
@@ -12686,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.168148908851852</v>
       </c>
     </row>
     <row r="1063">
@@ -12697,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.14230313038469</v>
       </c>
     </row>
     <row r="1064">
@@ -12730,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.268894993864842</v>
       </c>
     </row>
     <row r="1067">
@@ -12763,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.166156331162472</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1070">
@@ -12774,7 +12768,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.223115059195808</v>
       </c>
     </row>
     <row r="1071">
@@ -12829,7 +12823,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.338186249129367</v>
       </c>
     </row>
     <row r="1076">
@@ -12862,7 +12856,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.115810395460344</v>
       </c>
     </row>
     <row r="1079">
@@ -12950,7 +12944,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.76020718350716</v>
       </c>
     </row>
     <row r="1087">
@@ -12961,7 +12955,7 @@
         <v>16</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.251291056272199</v>
       </c>
     </row>
     <row r="1088">
@@ -12983,7 +12977,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.271607159958553</v>
       </c>
     </row>
     <row r="1090">
@@ -13049,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.305300694457046</v>
       </c>
     </row>
     <row r="1096">
@@ -13082,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.636469426254799</v>
       </c>
     </row>
     <row r="1099">
@@ -13093,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.222987960778916</v>
       </c>
     </row>
     <row r="1100">
@@ -13115,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.371776348480127</v>
       </c>
     </row>
     <row r="1102">
@@ -13137,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.202315266906818</v>
       </c>
     </row>
     <row r="1104">
@@ -13159,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.193445223142986</v>
       </c>
     </row>
     <row r="1106">
@@ -13192,7 +13186,7 @@
         <v>16</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.167609887623616</v>
+        <v>-0.150638499062659</v>
       </c>
     </row>
     <row r="1109">
@@ -13203,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.138673427878048</v>
       </c>
     </row>
     <row r="1110">
@@ -13225,7 +13219,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.193099862340594</v>
       </c>
     </row>
     <row r="1112">
@@ -13236,7 +13230,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.33476585072387</v>
       </c>
     </row>
     <row r="1113">
@@ -13269,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.191461534834881</v>
       </c>
     </row>
     <row r="1116">
@@ -13291,7 +13285,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.16687171404084</v>
       </c>
     </row>
     <row r="1118">
@@ -13357,7 +13351,7 @@
         <v>16</v>
       </c>
       <c r="C1123" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.159711040643953</v>
       </c>
     </row>
     <row r="1124">
@@ -13390,7 +13384,7 @@
         <v>16</v>
       </c>
       <c r="C1126" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.18430039214726</v>
       </c>
     </row>
     <row r="1127">
@@ -13401,7 +13395,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.365713259274147</v>
       </c>
     </row>
     <row r="1128">
@@ -13423,7 +13417,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.16983006497456</v>
       </c>
     </row>
     <row r="1130">
@@ -13445,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.208886494170025</v>
       </c>
     </row>
     <row r="1132">
@@ -13456,7 +13450,7 @@
         <v>16</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.202994543157078</v>
       </c>
     </row>
     <row r="1133">
@@ -13467,7 +13461,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.339326659336472</v>
       </c>
     </row>
     <row r="1134">
@@ -13489,7 +13483,7 @@
         <v>16</v>
       </c>
       <c r="C1135" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.184957939457712</v>
       </c>
     </row>
     <row r="1136">
@@ -13511,7 +13505,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0851209920048992</v>
       </c>
     </row>
     <row r="1138">
@@ -13555,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0852412837137797</v>
       </c>
     </row>
     <row r="1142">
@@ -13566,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.130483094757134</v>
       </c>
     </row>
     <row r="1143">
@@ -13599,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.145155753215658</v>
       </c>
     </row>
     <row r="1146">
@@ -13665,7 +13659,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.248021835040943</v>
       </c>
     </row>
     <row r="1152">
@@ -13676,7 +13670,7 @@
         <v>16</v>
       </c>
       <c r="C1152" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.102165767361553</v>
       </c>
     </row>
     <row r="1153">
@@ -13709,7 +13703,7 @@
         <v>16</v>
       </c>
       <c r="C1155" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.279675436340763</v>
       </c>
     </row>
     <row r="1156">
@@ -13731,7 +13725,7 @@
         <v>16</v>
       </c>
       <c r="C1157" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.235923082549154</v>
       </c>
     </row>
     <row r="1158">
@@ -13742,7 +13736,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.407004511736721</v>
       </c>
     </row>
     <row r="1159">
@@ -13775,7 +13769,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>-0.170230300067954</v>
+        <v>-0.430039913446718</v>
       </c>
     </row>
     <row r="1162">
@@ -13786,7 +13780,7 @@
         <v>16</v>
       </c>
       <c r="C1162" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.167460176128675</v>
       </c>
     </row>
     <row r="1163">
@@ -13819,7 +13813,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.11272495574834</v>
       </c>
     </row>
     <row r="1166">
@@ -13830,7 +13824,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.147556442146024</v>
+        <v>-0.179488560997895</v>
       </c>
     </row>
     <row r="1167">
@@ -13841,7 +13835,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.354106097075995</v>
       </c>
     </row>
     <row r="1168">
@@ -13863,7 +13857,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.19194737496516</v>
       </c>
     </row>
     <row r="1170">
@@ -13874,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.164139729459008</v>
+        <v>-0.231738337501396</v>
       </c>
     </row>
     <row r="1171">
@@ -13896,7 +13890,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.89181494943292</v>
       </c>
     </row>
     <row r="1173">
@@ -13907,7 +13901,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.219139407001182</v>
       </c>
     </row>
     <row r="1174">
@@ -13962,7 +13956,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.132616557420447</v>
       </c>
     </row>
     <row r="1179">
@@ -13984,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.307123249995652</v>
       </c>
     </row>
     <row r="1181">
@@ -14006,7 +14000,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.164812109998965</v>
       </c>
     </row>
     <row r="1183">
@@ -14028,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.284931053016599</v>
       </c>
     </row>
     <row r="1185">
@@ -14039,7 +14033,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.162757856352669</v>
+        <v>-0.187521010924714</v>
       </c>
     </row>
     <row r="1186">
@@ -14094,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.315656937125105</v>
       </c>
     </row>
     <row r="1191">
@@ -14105,7 +14099,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.238764479254695</v>
       </c>
     </row>
     <row r="1192">
@@ -14116,7 +14110,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.75484084479059</v>
       </c>
     </row>
     <row r="1193">
@@ -14127,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.160261204813932</v>
+        <v>-0.221424392796401</v>
       </c>
     </row>
     <row r="1194">
@@ -14138,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161548401088589</v>
       </c>
     </row>
     <row r="1195">
@@ -14160,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.188611184148721</v>
       </c>
     </row>
     <row r="1197">
@@ -14171,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.244925748836646</v>
       </c>
     </row>
     <row r="1198">
@@ -14182,7 +14176,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0722102219343079</v>
       </c>
     </row>
     <row r="1199">
@@ -14204,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.64602266911774</v>
       </c>
     </row>
     <row r="1201">
@@ -14215,7 +14209,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.182692921853425</v>
       </c>
     </row>
   </sheetData>
@@ -14532,7 +14526,7 @@
         <v>1757.71</v>
       </c>
       <c r="E18" t="n">
-        <v>-2809.75128764896</v>
+        <v>-336.555</v>
       </c>
     </row>
     <row r="19">
@@ -14787,7 +14781,7 @@
         <v>1517.85</v>
       </c>
       <c r="E33" t="n">
-        <v>-2629.90890426179</v>
+        <v>-73.0342857142858</v>
       </c>
     </row>
     <row r="34">
@@ -15025,7 +15019,7 @@
         <v>1.706</v>
       </c>
       <c r="E47" t="n">
-        <v>1.98066264525949</v>
+        <v>1.9909008682645</v>
       </c>
     </row>
     <row r="48">
@@ -15042,7 +15036,7 @@
         <v>4.218</v>
       </c>
       <c r="E48" t="n">
-        <v>1.34622479962988</v>
+        <v>1.4941596709884</v>
       </c>
     </row>
     <row r="49">
@@ -15059,7 +15053,7 @@
         <v>1.578</v>
       </c>
       <c r="E49" t="n">
-        <v>2.02023361234057</v>
+        <v>2.02805996274661</v>
       </c>
     </row>
     <row r="50">
@@ -15076,7 +15070,7 @@
         <v>3.683</v>
       </c>
       <c r="E50" t="n">
-        <v>1.94491337604056</v>
+        <v>1.85242857142857</v>
       </c>
     </row>
     <row r="51">
@@ -15093,7 +15087,7 @@
         <v>2.983</v>
       </c>
       <c r="E51" t="n">
-        <v>1.71151206781488</v>
+        <v>1.6528563904879</v>
       </c>
     </row>
     <row r="52">
@@ -15110,7 +15104,7 @@
         <v>2.44</v>
       </c>
       <c r="E52" t="n">
-        <v>2.10163029263175</v>
+        <v>1.96780499946956</v>
       </c>
     </row>
     <row r="53">
@@ -15161,7 +15155,7 @@
         <v>-1.918</v>
       </c>
       <c r="E55" t="n">
-        <v>2.2525</v>
+        <v>2.23022340063979</v>
       </c>
     </row>
     <row r="56">
@@ -15178,7 +15172,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>2.25437387254402</v>
+        <v>2.20847816994684</v>
       </c>
     </row>
     <row r="57">
@@ -15246,7 +15240,7 @@
         <v>1.311</v>
       </c>
       <c r="E60" t="n">
-        <v>2.09461460414992</v>
+        <v>2.04260927466876</v>
       </c>
     </row>
     <row r="61">
@@ -15263,7 +15257,7 @@
         <v>2.862</v>
       </c>
       <c r="E61" t="n">
-        <v>1.89969828774113</v>
+        <v>1.90895241143065</v>
       </c>
     </row>
     <row r="62">
@@ -15467,7 +15461,7 @@
         <v>25</v>
       </c>
       <c r="E73" t="n">
-        <v>42.5</v>
+        <v>42.010648294893</v>
       </c>
     </row>
     <row r="74">
@@ -15501,7 +15495,7 @@
         <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>45.2515310017776</v>
+        <v>46.9045323250367</v>
       </c>
     </row>
     <row r="76">
@@ -15976,13 +15970,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>15</v>
@@ -15993,13 +15987,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>15</v>
@@ -16016,7 +16010,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>15</v>
@@ -16033,7 +16027,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -16050,7 +16044,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
         <v>15</v>
@@ -16067,7 +16061,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
         <v>15</v>
@@ -16084,7 +16078,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -16101,7 +16095,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -16118,7 +16112,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" t="n">
         <v>15</v>
@@ -16135,7 +16129,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" t="n">
         <v>15</v>
@@ -16152,7 +16146,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D23" t="n">
         <v>15</v>
@@ -16163,13 +16157,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D24" t="n">
         <v>15</v>
@@ -16180,13 +16174,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D25" t="n">
         <v>15</v>
@@ -16197,13 +16191,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D26" t="n">
         <v>15</v>
@@ -16214,13 +16208,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D27" t="n">
         <v>15</v>
@@ -16237,7 +16231,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D28" t="n">
         <v>15</v>
@@ -16254,7 +16248,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D29" t="n">
         <v>15</v>
@@ -16271,7 +16265,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D30" t="n">
         <v>15</v>
@@ -16288,7 +16282,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D31" t="n">
         <v>15</v>
@@ -16305,7 +16299,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D32" t="n">
         <v>15</v>
@@ -16322,7 +16316,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D33" t="n">
         <v>15</v>
@@ -16339,7 +16333,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D34" t="n">
         <v>15</v>
@@ -16350,13 +16344,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D35" t="n">
         <v>15</v>
@@ -16367,13 +16361,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D36" t="n">
         <v>15</v>
@@ -16384,13 +16378,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D37" t="n">
         <v>15</v>
@@ -16401,13 +16395,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D38" t="n">
         <v>15</v>
@@ -16418,13 +16412,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D39" t="n">
         <v>15</v>
@@ -16435,13 +16429,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D40" t="n">
         <v>15</v>
@@ -16458,7 +16452,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D41" t="n">
         <v>15</v>
@@ -16475,7 +16469,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
         <v>15</v>
@@ -16492,7 +16486,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D43" t="n">
         <v>15</v>
@@ -16509,7 +16503,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D44" t="n">
         <v>15</v>
@@ -16526,7 +16520,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D45" t="n">
         <v>15</v>
@@ -16537,13 +16531,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D46" t="n">
         <v>15</v>
@@ -16554,13 +16548,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D47" t="n">
         <v>15</v>
@@ -16571,13 +16565,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D48" t="n">
         <v>15</v>
@@ -16588,13 +16582,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D49" t="n">
         <v>15</v>
@@ -16605,13 +16599,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D50" t="n">
         <v>15</v>
@@ -16622,13 +16616,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D51" t="n">
         <v>15</v>
@@ -16639,13 +16633,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D52" t="n">
         <v>15</v>
@@ -16656,13 +16650,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D53" t="n">
         <v>15</v>
@@ -16679,7 +16673,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D54" t="n">
         <v>15</v>
@@ -16696,7 +16690,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
         <v>15</v>
@@ -16713,7 +16707,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D56" t="n">
         <v>15</v>
@@ -16724,16 +16718,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -16741,16 +16735,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -16758,16 +16752,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -16775,16 +16769,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -16792,16 +16786,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
         <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -16809,16 +16803,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -16826,16 +16820,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -16843,16 +16837,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
         <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -16860,16 +16854,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
         <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D65" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -16877,16 +16871,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
         <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -16900,216 +16894,12 @@
         <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D67" t="n">
         <v>14</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" t="n">
-        <v>14</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" t="n">
-        <v>14</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>21</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="s">
-        <v>46</v>
-      </c>
-      <c r="D70" t="n">
-        <v>14</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="s">
-        <v>47</v>
-      </c>
-      <c r="D71" t="n">
-        <v>14</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>48</v>
-      </c>
-      <c r="D72" t="n">
-        <v>14</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D73" t="n">
-        <v>14</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" t="n">
-        <v>14</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>21</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="s">
-        <v>51</v>
-      </c>
-      <c r="D75" t="n">
-        <v>14</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="s">
-        <v>52</v>
-      </c>
-      <c r="D76" t="n">
-        <v>14</v>
-      </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="s">
-        <v>53</v>
-      </c>
-      <c r="D77" t="n">
-        <v>14</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="s">
-        <v>54</v>
-      </c>
-      <c r="D78" t="n">
-        <v>14</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="s">
-        <v>55</v>
-      </c>
-      <c r="D79" t="n">
-        <v>14</v>
-      </c>
-      <c r="E79" t="n">
         <v>1</v>
       </c>
     </row>
